--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="436">
   <si>
     <t>id</t>
   </si>
@@ -4563,6 +4563,311 @@
 from something's waste.
 That's just
 how humans are.</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>刀集めのサダ</t>
+  </si>
+  <si>
+    <t>Sada the Sword Collector</t>
+  </si>
+  <si>
+    <t>26.09.09</t>
+  </si>
+  <si>
+    <t>火星への侵攻が始まって
+三ヶ月が経った
+平地は戦車部隊
+山岳地帯は
+我々昆虫部隊の担当だ
+多脚型は岩場に強い
+少しくらい崖があっても
+こいつなら問題なく進める
+ガシャ
+ガシャ
+サダさん
+また刀増えてません？
+ああ
+昨日一本拾った
+火星に刀なんてあるんですね
+あるよ
+地球より多い
+後ろに乗っているのは
+刀集めのサダ
+戦闘が終わるたび
+どこからか刀を拾ってくる
+それで何本目です？
+二百七十三
+地球に持って帰るんですか？
+いや
+全部火星産だ
+地球に持って帰ったら
+おかしいだろ
+……
+その日の夕方
+岩場でまた一本見つかった
+サダさん
+これ
+柄に名前が彫ってありますよ
+サダ
+……
+ああ
+やっと見つけた
+俺のだ</t>
+  </si>
+  <si>
+    <t>The invasion of Mars began
+three months ago
+The tank units handle the plains
+The mountain regions
+are our insect unit's territory
+Multi-legged models are good on rocky terrain
+Even with a few cliffs
+this thing gets through just fine
+CLANK
+CLANK
+Sada
+Haven't you got more swords again?
+Yeah
+Found one yesterday
+There are swords on Mars?
+Sure
+More than on Earth
+The man riding behind me
+is Sada the Sword Collector
+Every time a battle ends
+he comes back with a sword from somewhere
+How many does that make?
+Two hundred seventy-three
+Are you taking them back to Earth?
+No
+They're all Martian-made
+It'd be weird
+to take them back to Earth
+...
+That evening
+we found another one among the rocks
+Sada
+Look at this
+There's a name carved into the hilt
+Sada
+...
+Yeah
+Finally found it
+It's mine</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>人間界方面</t>
+  </si>
+  <si>
+    <t>Toward the Human World</t>
+  </si>
+  <si>
+    <t>26.09.10</t>
+  </si>
+  <si>
+    <t>人間界へ行くには
+このエスカレーターに乗る
+別に珍しいものじゃない
+毎朝みんな
+ここから仕事へ向かう
+ゴウンゴウン
+乗っている間に
+体は少しずつ人間へ変わっていく
+鱗が消えて
+腕が二本になって
+目も二つになる
+上にいた頃はあんな姿だった連中も
+下へ着く頃には立派な会社員だ
+私ももう十年以上使っている
+ネクタイまで勝手に出てくるから
+なかなか便利なものだ
+ただ
+たまに変換の遅いやつがいる
+おいまだ尻尾残ってるぞ
+え
+本当ですか
+まあいい
+ズボンに入れとけ
+遅刻するぞ
+……
+今日も人間界は朝から忙しいのだ</t>
+  </si>
+  <si>
+    <t>To get to the human world,
+you take this escalator.
+It’s nothing unusual.
+Every morning,
+everyone heads to work from here.
+Rumble, rumble.
+As you ride,
+your body gradually transforms into a human one.
+Your scales disappear.
+Your arms become two.
+Your eyes become two.
+Even those who looked like that up above
+are perfectly respectable office workers by the time they reach the bottom.
+I’ve been using it myself for over ten years now.
+It even gives you a necktie automatically,
+so it’s pretty convenient.
+Though sometimes,
+you get someone whose transformation is a little slow.
+Hey,
+you’ve still got a tail.
+Huh?
+Really?
+Ah, whatever.
+Just tuck it into your pants.
+You’re gonna be late.
+...
+Another busy morning in the human world.</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>人類保護区</t>
+  </si>
+  <si>
+    <t>Human Reserve</t>
+  </si>
+  <si>
+    <t>26.09.17</t>
+  </si>
+  <si>
+    <t>「人類は絶滅させてはならない。
+しかし、文明を持たせてもならない。」
+それが彼らの決めたルールだ
+人類が地球を壊しかけたあの日から
+二万年以上が経った
+今では我々も
+洞窟での暮らしにすっかり慣れた
+食料は毎朝ここで配給される
+病気になれば治してくれるし
+危険な生物も近づいてこない
+昔よりずっと安全らしい
+ただし
+文明を使うには彼らの許可がいる
+火
+文字
+農耕
+車輪
+人間が昔使っていたものを
+一つずつ申請する
+申請に使えるのは
+戦争を生き残ったこの端末だけだ
+カタカタ
+お
+車輪の申請どうだった？
+まだ審査中
+今年こそ通ると思ったんだけどな
+無理だろ
+去年
+隣の集落が二輪車作ったからな
+あれでまた百年延びたらしいぞ
+マジか
+一輪にしとけばよかったのにな
+……
+まあいい
+芋もらって帰ろう
+人類が火を取り戻すまで
+あと四百二十七年
+人類は今日も
+順調に保護されている</t>
+  </si>
+  <si>
+    <t>“Humanity must not be allowed to go extinct.
+But neither must it be allowed to have civilization.”
+That is the rule they established.
+More than twenty thousand years have passed
+since the day humanity nearly destroyed the Earth.
+By now,
+we’ve grown quite used to living in caves.
+Food is distributed here every morning.
+If we get sick, they heal us.
+Dangerous creatures are kept away.
+Apparently, life is much safer than it used to be.
+There is just one condition.
+To use anything from civilization,
+we need their permission.
+Fire.
+Writing.
+Agriculture.
+The wheel.
+Everything humans once used
+must be applied for, one by one.
+And this terminal,
+the only one that survived the war,
+is the only place we can submit an application.
+Clack clack.
+Hey.
+What happened with the application for the wheel?
+Still under review.
+I thought it might finally get approved this year.
+No chance.
+Last year,
+the settlement next door built a two-wheeled vehicle.
+Apparently that set us back another hundred years.
+Seriously?
+They should’ve just stuck with one wheel.
+...
+Oh well.
+Let’s get our potatoes and go home.
+Until humanity is allowed to use fire again:
+427 years.
+Humanity remains,
+as always, safely under protection.</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>ピーマンBeatbox</t>
+  </si>
+  <si>
+    <t>Bell Pepper Beatbox</t>
+  </si>
+  <si>
+    <t>26.09.20</t>
+  </si>
+  <si>
+    <t>時間はかかったが
+ようやく私のクローンが完成した
+完璧だ
+これなら街を歩いても
+誰も私のクローンだとは気づくまい
+ピーマン型ラボの中で
+男は秘密の研究を続けていた
+ヘリコプターが飛び
+巨大な操作の手が
+もうすぐそこまで伸びてきていることも知らず
+ドゥビドゥビドゥ
+ズッタッタウンタッタ
+ピーマン beatbox
+奇怪な愉快犯が
+今日も唸るのだ</t>
+  </si>
+  <si>
+    <t>It took some time,
+but at last, my clone is complete.
+Perfect.
+Now I can walk through the city
+and no one will ever know he’s my clone.
+Inside a bell pepper-shaped lab,
+the man continued his secret research.
+A helicopter flew overhead,
+unaware that a giant hand
+was already reaching in to manipulate him.
+Dooby-dooby-doo
+Zutta-tatta-unta-tta
+Bell Pepper Beatbox
+The bizarre prankster
+rumbles on again today.</t>
   </si>
 </sst>
 </file>
@@ -7582,12 +7887,24 @@
       <c r="Y70" s="3"/>
     </row>
     <row r="71">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="A71" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>417</v>
+      </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -7609,12 +7926,24 @@
       <c r="Y71" s="3"/>
     </row>
     <row r="72">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="A72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>423</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -7636,12 +7965,24 @@
       <c r="Y72" s="3"/>
     </row>
     <row r="73">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+      <c r="A73" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>429</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -7663,12 +8004,24 @@
       <c r="Y73" s="3"/>
     </row>
     <row r="74">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="A74" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>435</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>

--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="442">
   <si>
     <t>id</t>
   </si>
@@ -4868,6 +4868,64 @@
 Bell Pepper Beatbox
 The bizarre prankster
 rumbles on again today.</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>美妙</t>
+  </si>
+  <si>
+    <t>Strangely Delicious</t>
+  </si>
+  <si>
+    <t>26.09.22</t>
+  </si>
+  <si>
+    <t>くんくん
+確かこのあたりから香ってるんだけどな
+今日はセンサーが鈍い気がする
+まあ
+70年代のセンサーだから仕方ない
+私はモグラ型機械をゆっくり進めた
+この辺りは地上との距離が近い
+あ、いた
+店長へ連絡しておこう
+このサイズなら十人前にはなりそうだ
+...
+自分たちが普段垂れ流しているものが
+まさか食材になって地中にいるなんて
+人間達は考えもしないだろうな
+美味じゃなくて美妙なのだ
+世界は
+食って
+出して
+また食っている</t>
+  </si>
+  <si>
+    <t>Sniff, sniff.
+I'm sure the smell is coming from around here.
+The sensor seems a little dull today.
+Well,
+it's from the '70s.
+Can't really blame it.
+I slowly moved the mole machine forward.
+We're pretty close to the surface around here.
+Ah, there it is.
+Better let the manager know.
+At this size,
+it should make about ten servings.
+...
+Humans would never imagine
+that what they casually let out every day
+ends up underground
+and becomes food.
+It's not just delicious.
+It's mysteriously delicious.
+The world
+eats,
+lets it out,
+and eats again.</t>
   </si>
 </sst>
 </file>
@@ -8043,12 +8101,24 @@
       <c r="Y74" s="3"/>
     </row>
     <row r="75">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="A75" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
